--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>訂單ID</t>
   </si>
@@ -105,6 +105,21 @@
   </si>
   <si>
     <t>鴨肉羹 (大)*1 麻醬乾麵 (大)*1</t>
+  </si>
+  <si>
+    <t>2026/7/12 上午11:20:02</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>測試員</t>
+  </si>
+  <si>
+    <t>健康低脂鹹豬肉*1</t>
+  </si>
+  <si>
+    <t>正常 (不調整)</t>
   </si>
   <si>
     <t>店家/品項名稱</t>
@@ -519,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -687,6 +702,32 @@
         <v>140</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>1783826402483</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -695,7 +736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -704,10 +745,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -747,6 +788,14 @@
         <v>30</v>
       </c>
       <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>

--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -107,7 +107,7 @@
     <t>鴨肉羹 (大)*1 麻醬乾麵 (大)*1</t>
   </si>
   <si>
-    <t>2026/7/12 上午11:20:02</t>
+    <t>2026/7/12 下午8:29:09</t>
   </si>
   <si>
     <t>TEST</t>
@@ -704,7 +704,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>1783826402483</v>
+        <v>1783859349392</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>

--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="72">
   <si>
     <t>訂單ID</t>
   </si>
@@ -120,6 +120,108 @@
   </si>
   <si>
     <t>正常 (不調整)</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:31:53</t>
+  </si>
+  <si>
+    <t>香腸飯*1</t>
+  </si>
+  <si>
+    <t>正常（加醬汁、加蔥油）</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:36:43</t>
+  </si>
+  <si>
+    <t>12218</t>
+  </si>
+  <si>
+    <t>沈佩琪</t>
+  </si>
+  <si>
+    <t>油雞腿飯*1 脆皮燒肉飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:40:25</t>
+  </si>
+  <si>
+    <t>燒鴨腿 (一隻)*1 脆皮燒肉飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:43:50</t>
+  </si>
+  <si>
+    <t>燒鴨腿 (一隻)*1 四寶飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:44:29</t>
+  </si>
+  <si>
+    <t>四寶飯*1 脆皮燒肉 (一份)*1</t>
+  </si>
+  <si>
+    <t>多醬汁</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:59:12</t>
+  </si>
+  <si>
+    <t>12996</t>
+  </si>
+  <si>
+    <t>鄭雅君</t>
+  </si>
+  <si>
+    <t>油雞腿飯*1 燒雞腿飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 上午9:59:48</t>
+  </si>
+  <si>
+    <t>脆皮燒肉飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 下午7:45:41</t>
+  </si>
+  <si>
+    <t>照燒雞腿便當*1 現烤香腸*1</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>2026/7/13 下午8:04:17</t>
+  </si>
+  <si>
+    <t>厚燒排骨便當*1 激安A組合 (現烤香腸 + 精選湯品 大骨竹筍湯(夏季供應))*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 下午8:07:01</t>
+  </si>
+  <si>
+    <t>招牌燒肉便當*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 下午8:13:58</t>
+  </si>
+  <si>
+    <t>厚燒排骨便當*1 現烤香腸*1 現煎荷包蛋*1</t>
+  </si>
+  <si>
+    <t>2026/7/13 下午8:47:21</t>
+  </si>
+  <si>
+    <t>10069</t>
+  </si>
+  <si>
+    <t>許民芳</t>
+  </si>
+  <si>
+    <t>泡菜燒肉便當*1 激安A組合 (現烤香腸 + 精選湯品 大骨竹筍湯(夏季供應))*1</t>
+  </si>
+  <si>
+    <t>2026/7/14 上午7:56:42</t>
   </si>
   <si>
     <t>店家/品項名稱</t>
@@ -534,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -728,6 +830,344 @@
         <v>110</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1783906313042</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1783906603701</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1783906825272</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1783907030943</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1783907069841</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1783907952892</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1783907988623</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>1783943141314</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>1783944257776</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>1783944421511</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>1783944838131</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>1783946841084</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>1783987002730</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="3">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -736,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -745,10 +1185,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -796,6 +1236,102 @@
         <v>34</v>
       </c>
       <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="3">
         <v>1</v>
       </c>
     </row>

--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="261">
   <si>
     <t>訂單ID</t>
   </si>
@@ -107,21 +107,6 @@
     <t>鴨肉羹 (大)*1 麻醬乾麵 (大)*1</t>
   </si>
   <si>
-    <t>2026/7/12 下午8:29:09</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>測試員</t>
-  </si>
-  <si>
-    <t>健康低脂鹹豬肉*1</t>
-  </si>
-  <si>
-    <t>正常 (不調整)</t>
-  </si>
-  <si>
     <t>2026/7/13 上午9:31:53</t>
   </si>
   <si>
@@ -222,6 +207,588 @@
   </si>
   <si>
     <t>2026/7/14 上午7:56:42</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午4:02:39</t>
+  </si>
+  <si>
+    <t>雞豬都吃 (松阪豬+雞肉+任6菜)*1 豆皮(炸)*1 米血*1 雞翅*1 豆干絲(麵)*1 豬耳朵絲*1 玉米筍*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:正常 | 辣度:不辣 | 配菜:筍片 | 調味:蔥 | 盒裝:需要 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午4:02:49</t>
+  </si>
+  <si>
+    <t>雞豬都吃 (松阪豬+雞肉+任6菜)*1 高麗菜*1 玉米筍*1 白蘿蔔*1 杏鮑菇*1 泡麵*1 豆包(無炸)*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:多口 | 辣度:不辣 | 配菜:筍片 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午4:10:27</t>
+  </si>
+  <si>
+    <t>雞豬都吃 (松阪豬+雞肉+任6菜)*1 單點鹽水腿*1 龍鬚菜*1 玉米筍*1 小黃瓜*1 白蘿蔔*1 米血*1 甜不辣*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:少口 | 辣度:微微 | 配菜:洋蔥 | 調味:蔥,蒜,檸檬 | 盒裝:需要 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午4:49:39</t>
+  </si>
+  <si>
+    <t>套餐 (舒肥胸 + 任2小菜)*1 米血*1 綠花椰*1 玉米筍*1 白蘿蔔*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:多口 | 辣度:不辣 | 配菜:洋蔥 | 調味:蒜 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午4:50:48</t>
+  </si>
+  <si>
+    <t>601473</t>
+  </si>
+  <si>
+    <t>李羽茹</t>
+  </si>
+  <si>
+    <t>魚豆腐*1 套餐 (鹽水腿 + 任2小菜)*1 米血*1 高麗菜*1 小黃瓜*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:正常 | 辣度:微微 | 配菜:筍片 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/14 下午7:44:17</t>
+  </si>
+  <si>
+    <t>套餐 (鹽水腿 + 任2小菜)*1 豆包(無炸)*1 水晶藻*1 蓮藕*1 高麗菜*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:少口 | 辣度:不辣 | 配菜:筍片,洋蔥 | 調味:蔥少,蒜少 | 盒裝:需要 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/15 上午8:08:08</t>
+  </si>
+  <si>
+    <t>6513</t>
+  </si>
+  <si>
+    <t>李承州</t>
+  </si>
+  <si>
+    <t>米血*1 甜不辣*1 豆包(無炸)*1 百頁豆腐*1</t>
+  </si>
+  <si>
+    <t>口味細節：【口味】胡椒:正常 | 辣度:微微 | 配菜:筍片 | 調味:蔥,蒜,檸檬 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/15 下午6:40:58</t>
+  </si>
+  <si>
+    <t>瓜仔肉飯*1 味噌湯*1</t>
+  </si>
+  <si>
+    <t>2026/7/15 下午8:10:12</t>
+  </si>
+  <si>
+    <t>爌肉飯*1 味噌蛋花湯*1 嘴邊肉*1 肝連*1 特嫩油豆腐*1</t>
+  </si>
+  <si>
+    <t>2026/7/15 下午8:19:19</t>
+  </si>
+  <si>
+    <t>爌肉飯*1 魯蛋*1</t>
+  </si>
+  <si>
+    <t>【外帶】肥瘦偏好:適中 | 醬汁飯量:多醬汁 | 辣度:不辣 | 備註：無</t>
+  </si>
+  <si>
+    <t>2026/7/15 下午9:11:51</t>
+  </si>
+  <si>
+    <t>爌肉飯*1 小菜-豬腳 (中段)*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 上午9:00:02</t>
+  </si>
+  <si>
+    <t>爌肉飯*1 燙青菜*1 筍乾*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:34:37</t>
+  </si>
+  <si>
+    <t>11744</t>
+  </si>
+  <si>
+    <t>施名娟</t>
+  </si>
+  <si>
+    <t>金針菇*1 生豆包*2 木耳*1 花椰菜*1</t>
+  </si>
+  <si>
+    <t>小辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:36:45</t>
+  </si>
+  <si>
+    <t>13228</t>
+  </si>
+  <si>
+    <t>宋筱湄</t>
+  </si>
+  <si>
+    <t>河粉*1 鴨米血*1 大豆干*1 大陸妹*1 甜不辣*1</t>
+  </si>
+  <si>
+    <t>微辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:37:30</t>
+  </si>
+  <si>
+    <t>空心菜*1 王子麵*1 炸豆皮*1 米血*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:41:05</t>
+  </si>
+  <si>
+    <t>豬肉片*2 河粉*1 菜頭*1 豆芽菜*1 大陸妹*1 玉米筍*1 高麗菜*1 金針菇*1 千張皮*1 德式香腸*1</t>
+  </si>
+  <si>
+    <t>不辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:41:17</t>
+  </si>
+  <si>
+    <t>菜頭*1 花椰菜*1 黑輪*1 甜不辣*1 百頁豆腐*1 鳥蛋*1 米血*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:41:22</t>
+  </si>
+  <si>
+    <t>豆芽菜*1 金針菇*1 香菇*1 豬肉片*1 小豆干*2 米血*1 黑輪*1 炸豆皮(條)*1 蝦捲*1 貢丸*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:43:01</t>
+  </si>
+  <si>
+    <t>百頁豆腐*1 鑫鑫腸*1 炸豆皮(條)*1 豬肉片*1 關廟麵*1 高麗菜*1 豬耳朵*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:50:03</t>
+  </si>
+  <si>
+    <t>空心菜*1 王子麵*1 芋條*1 韓式年糕/3個*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:52:12</t>
+  </si>
+  <si>
+    <t>11258</t>
+  </si>
+  <si>
+    <t>鄭秋燕</t>
+  </si>
+  <si>
+    <t>高麗菜*1 玉米筍*1 水晶餃*1 蘭花干*1 韓式Q拉麵*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午4:59:13</t>
+  </si>
+  <si>
+    <t>豆芽菜*1 菜頭*1 高麗菜*1 蒟蒻/3個*1 生豆包*1 冬粉*1 豬肉片*1</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午5:02:44</t>
+  </si>
+  <si>
+    <t>6154</t>
+  </si>
+  <si>
+    <t>許庭芬</t>
+  </si>
+  <si>
+    <t>金針菇*1 花椰菜*1 王子麵*1</t>
+  </si>
+  <si>
+    <t>不加酸菜 / 辣度:不辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午5:03:15</t>
+  </si>
+  <si>
+    <t>12757</t>
+  </si>
+  <si>
+    <t>黃娉娟</t>
+  </si>
+  <si>
+    <t>空心菜*1 玉米筍*1 雪菇*1 蝦捲*1 蘭花干*1 炸豆腐/2個*1 關廟麵*1 貢丸*1</t>
+  </si>
+  <si>
+    <t>要加酸菜 / 辣度:微辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午5:09:20</t>
+  </si>
+  <si>
+    <t>11110</t>
+  </si>
+  <si>
+    <t>林佳蘭</t>
+  </si>
+  <si>
+    <t>生豆包*1 高麗菜*1 金針菇*1 王子麵*1</t>
+  </si>
+  <si>
+    <t>要加酸菜 / 辣度:不辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午5:21:45</t>
+  </si>
+  <si>
+    <t>15150</t>
+  </si>
+  <si>
+    <t>黃珮瑄</t>
+  </si>
+  <si>
+    <t>高麗菜*1 蒸煮麵*1 米血*1 生豆包*1 炸豆皮*1 大豆干*1 芋條*1</t>
+  </si>
+  <si>
+    <t>要加酸菜 / 辣度:小辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午8:03:54</t>
+  </si>
+  <si>
+    <t>13266</t>
+  </si>
+  <si>
+    <t>梁薽予</t>
+  </si>
+  <si>
+    <t>豆芽菜*1 高麗菜*1 鳥蛋*1 米血*1 千張皮*1 雪菇*1</t>
+  </si>
+  <si>
+    <t>不加酸菜 / 辣度:微辣</t>
+  </si>
+  <si>
+    <t>2026/7/16 下午8:57:59</t>
+  </si>
+  <si>
+    <t>水蓮*1 櫛瓜*1 鳥蛋*1 冬粉*1 米血*1 韓式魚板*1</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:27:38</t>
+  </si>
+  <si>
+    <t>土魠魚羹飯*1 燙青菜*1</t>
+  </si>
+  <si>
+    <t>份量:正常份量 / 辣度:微辣 / 總計:$130  (備註: 羹飯醋多)</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:28:11</t>
+  </si>
+  <si>
+    <t>羊肉羹飯*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:不辣 / 總計:$90 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:28:42</t>
+  </si>
+  <si>
+    <t>土魠魚羹飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:34:08</t>
+  </si>
+  <si>
+    <t>乾麵*1 皮蛋豆腐*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:微辣 / 總計:$90 </t>
+  </si>
+  <si>
+    <t>羊肉羹麵*1</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:36:43</t>
+  </si>
+  <si>
+    <t>土魠魚羹米粉*1</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:36:44</t>
+  </si>
+  <si>
+    <t>15440</t>
+  </si>
+  <si>
+    <t>施欣玫</t>
+  </si>
+  <si>
+    <t>土魠魚羹麵*1</t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:37:21</t>
+  </si>
+  <si>
+    <t>豬排特餐*1 米血*1 土魠魚酥*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:不辣 / 總計:$255 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:37:39</t>
+  </si>
+  <si>
+    <t>燙青菜*1 土魠魚羹飯*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:不辣 / 總計:$130 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:40:49</t>
+  </si>
+  <si>
+    <t>魚酥特餐*1 燙青菜*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:不辣 / 總計:$165 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:51:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:微辣 / 總計:$130 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:53:22</t>
+  </si>
+  <si>
+    <t>16508</t>
+  </si>
+  <si>
+    <t>尹語璟</t>
+  </si>
+  <si>
+    <t>豬排飯*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:正常份量 / 辣度:微辣 / 總計:$80 </t>
+  </si>
+  <si>
+    <t>2026/7/20 上午10:58:24</t>
+  </si>
+  <si>
+    <t>日式豬排特餐*1 炸百頁豆腐*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">份量:羹類/飯麵加份量(+15元) / 辣度:不辣 / 總計:$160 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:22:29</t>
+  </si>
+  <si>
+    <t>腿庫皮便當*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:多醬汁 / 辣度:不辣 / 總計:$100 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:23:23</t>
+  </si>
+  <si>
+    <t>魯肉便當*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:正常 / 辣度:不辣 / 總計:$80 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:23:45</t>
+  </si>
+  <si>
+    <t>隔間肉湯*1 隔間肉 (單點小菜)*1 爌肉飯*1 爌肉 (單點小菜)*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:偏瘦 / 醬汁:正常 / 辣度:不辣 / 總計:$240 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:23:57</t>
+  </si>
+  <si>
+    <t>腿庫皮便當*1 爌肉 (單點小菜)*1 白菜魯*1 魯油豆腐*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:多醬汁 / 辣度:不辣 / 總計:$225 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:26:58</t>
+  </si>
+  <si>
+    <t>豬腳便當 (有肉頭段)*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:多醬汁 / 辣度:不辣 / 總計:$145 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:27:19</t>
+  </si>
+  <si>
+    <t>加辣</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:多醬汁 / 辣度:加辣 / 總計:$85 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:27:57</t>
+  </si>
+  <si>
+    <t>魯肉飯*1 魯蛋*1 燙青菜*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:偏瘦 / 醬汁:少醬汁 / 辣度:加辣 / 總計:$105 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:28:05</t>
+  </si>
+  <si>
+    <t>601207</t>
+  </si>
+  <si>
+    <t>郭勝明</t>
+  </si>
+  <si>
+    <t>爌肉便當*1 虱目魚丸湯*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:偏瘦 / 醬汁:正常 / 辣度:加辣 / 總計:$150 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午5:29:56</t>
+  </si>
+  <si>
+    <t>爌肉便當*1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:適中 / 醬汁:正常 / 辣度:不辣 / 總計:$100 </t>
+  </si>
+  <si>
+    <t>2026/7/20 下午8:32:14</t>
+  </si>
+  <si>
+    <t>2026/7/21 上午8:14:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肥瘦:偏肥 / 醬汁:多醬汁 / 辣度:加辣 / 總計:$100 </t>
+  </si>
+  <si>
+    <t>2026/7/22 下午4:54:09</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：豬肉片*1 蟹肉棒 (3個)*1 貢丸 (3顆)*1 豆皮 (1塊)*1 黑輪 (1條)*1 手作肉丸 (1顆)*1 甜不辣 (1片)*1 米血糕 (1片)*1 魚豆腐 (3個)*1 龍蝦沙拉 (3顆)*1</t>
+  </si>
+  <si>
+    <t>湯與醬都要</t>
+  </si>
+  <si>
+    <t>醬料/辣度：湯與醬都要 / 總計：$200</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午4:56:19</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：黯然消魂麵 (微辣)*1 時蔬*1 豆皮 (1塊)*1 白蘿蔔*1 香菇*1 貢丸 (3顆)*1 三角油豆腐 (3個)*1 甜不辣 (1片)*1</t>
+  </si>
+  <si>
+    <t>關東煮要加湯</t>
+  </si>
+  <si>
+    <t>醬料/辣度：關東煮要加湯 / 總計：$200</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午4:58:53</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：黯然消魂麵 (微辣)*1</t>
+  </si>
+  <si>
+    <t>正常 (附關東煮沾醬)</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附關東煮沾醬) / 總計：$80</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午5:01:35</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：米血糕 (1片) (湯)*2 百頁豆腐 (2個) (湯)*1 白蘿蔔 (湯)*1 甜不辣 (1片) (湯)*1 黑輪 (1條) (湯)*1</t>
+  </si>
+  <si>
+    <t>正常 (附沾醬/原味)</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附沾醬/原味) / 總計：$70</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午5:02:34</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：豬肉片*1 炒泡麵 (豬肉)*1 時蔬*1 貢丸 (3顆)*1 豆皮 (1塊)*1 鑫鑫腸 (3個)*1</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午5:04:33</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：日式炒烏龍麵*1</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附關東煮沾醬) / 總計：$85</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午5:07:59</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：黯然消魂麵 (微辣)*1 三角油豆腐 (3個) (湯)*1 杏鮑菇 (湯)*1</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附沾醬/原味) / 總計：$100</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午8:02:13</t>
+  </si>
+  <si>
+    <t>要加辣</t>
+  </si>
+  <si>
+    <t>醬料/辣度：要加辣 / 總計：$85</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午8:45:19</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：日式炒烏龍麵 (湯)*1</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附沾醬/原味) / 總計：$85</t>
+  </si>
+  <si>
+    <t>2026/7/22 下午9:07:19</t>
+  </si>
+  <si>
+    <t>顏舍關東煮：金針菇 (湯)*1 豆皮 (1塊) (湯)*1 冬粉 (湯)*1 三角油豆腐 (3個) (湯)*1 百頁豆腐 (2個) (湯)*1 米血糕 (1片) (湯)*1 魚餃 (2個) (湯)*1 豬肉片 (湯)*1 黑輪 (1條) (湯)*1 白蘿蔔 (湯)*1</t>
+  </si>
+  <si>
+    <t>醬料/辣度：正常 (附沾醬/原味) / 總計：$165</t>
   </si>
   <si>
     <t>店家/品項名稱</t>
@@ -636,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -806,74 +1373,74 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>1783859349392</v>
+        <v>1783906313042</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="3">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>1783906313042</v>
+        <v>1783906603701</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="3">
-        <v>80</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>1783906603701</v>
+        <v>1783906825272</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -884,114 +1451,114 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>1783906825272</v>
+        <v>1783907030943</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="3">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>1783907030943</v>
+        <v>1783907069841</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="3">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>1783907069841</v>
+        <v>1783907952892</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="3">
-        <v>260</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>1783907952892</v>
+        <v>1783907988623</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H13" s="3">
-        <v>200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>1783907988623</v>
+        <v>1783943141314</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>24</v>
@@ -1000,172 +1567,1758 @@
         <v>25</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="H14" s="3">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>1783943141314</v>
+        <v>1783944257776</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H15" s="3">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>1783944257776</v>
+        <v>1783944421511</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3">
-        <v>160</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>1783944421511</v>
+        <v>1783944838131</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H17" s="3">
-        <v>99</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>1783944838131</v>
+        <v>1783946841084</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H18" s="3">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>1783946841084</v>
+        <v>1783987002730</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H19" s="3">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>1783987002730</v>
+        <v>1784016159609</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>1784016169384</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="F21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>1784016627052</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="E22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>1784018979937</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>1784019048502</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>1784029457300</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>1784074088713</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>1784112058800</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>1784117412899</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>1784117959418</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>1784121111183</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>1784163602101</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>1784190877474</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>1784191005915</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>1784191050135</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>1784191265692</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>1784191277219</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>1784191282160</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>1784191381102</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>1784191803020</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>1784191932463</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>1784192353587</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>1784192564980</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H42" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>1784192595486</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>1784192960377</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H44" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>1784193705984</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H45" s="3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>1784203434532</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H46" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>1784206679193</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>1784514458683</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H48" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>1784514491802</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>160</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H49" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>1784514522957</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H50" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>1784514848289</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>1784514848328</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H52" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>1784515003726</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>1784515004617</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H54" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>1784515041766</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H55" s="3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>1784515059692</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H56" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>1784515249111</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H57" s="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>1784515913682</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H58" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>1784516002538</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H59" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>1784516304449</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H60" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>1784539349837</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>1784539403829</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H62" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>1784539425009</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H63" s="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>1784539437641</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H64" s="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>1784539618911</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>1784539639360</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>1784539677418</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H67" s="3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>1784539685646</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H68" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>1784539796659</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H69" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>1784550734914</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>1784592862048</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H71" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>1784710449306</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H72" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>1784710579215</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H73" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>1784710733864</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H74" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>1784710895853</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H75" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>1784710954725</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H76" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>1784711073676</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H77" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>1784711279120</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H78" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>1784721733218</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H79" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>1784724319920</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H80" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>1784725639387</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H81" s="3">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +3329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1185,10 +3338,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1233,7 +3386,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1249,7 +3402,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1257,7 +3410,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1265,7 +3418,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -1281,7 +3434,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -1289,7 +3442,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -1297,23 +3450,23 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
@@ -1321,7 +3474,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1329,9 +3482,457 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B75" s="3">
         <v>1</v>
       </c>
     </row>

--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>訂單ID</t>
   </si>
@@ -36,6 +36,87 @@
   </si>
   <si>
     <t>金額</t>
+  </si>
+  <si>
+    <t>2026/7/29 上午7:53:37</t>
+  </si>
+  <si>
+    <t>601471</t>
+  </si>
+  <si>
+    <t>陳永育</t>
+  </si>
+  <si>
+    <t>羹香鴨肉羹：麻醬乾麵 (大)*1 鴨肉羹 (小)*1</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>小菜項目：無 / 醬料/辣度：正常 / 總計：$130</t>
+  </si>
+  <si>
+    <t>2026/7/29 上午7:55:57</t>
+  </si>
+  <si>
+    <t>18445</t>
+  </si>
+  <si>
+    <t>李珈豪</t>
+  </si>
+  <si>
+    <t>羹香鴨肉羹：鴨肉羹麵 (小)*1</t>
+  </si>
+  <si>
+    <t>加醋</t>
+  </si>
+  <si>
+    <t>小菜項目：無 / 醬料/辣度：加醋 / 總計：$70</t>
+  </si>
+  <si>
+    <t>2026/7/29 上午8:05:51</t>
+  </si>
+  <si>
+    <t>16661</t>
+  </si>
+  <si>
+    <t>陳育倫</t>
+  </si>
+  <si>
+    <t>羹香鴨肉羹：醋香乾麵 (大)*1 鴨肉羹 (大)*1 精選小菜 (兩盒優惠)*1</t>
+  </si>
+  <si>
+    <t>小菜項目：黃金泡菜、豬頭皮 / 醬料/辣度：正常 / 總計：$175</t>
+  </si>
+  <si>
+    <t>2026/7/29 上午8:06:16</t>
+  </si>
+  <si>
+    <t>10047</t>
+  </si>
+  <si>
+    <t>許博捷</t>
+  </si>
+  <si>
+    <t>羹香鴨肉羹：麻辣乾麵 (大)*1 燙地瓜葉*1 鴨肉羹 (大)*1</t>
+  </si>
+  <si>
+    <t>小菜項目：無 / 醬料/辣度：正常 / 總計：$155</t>
+  </si>
+  <si>
+    <t>2026/7/29 上午8:16:39</t>
+  </si>
+  <si>
+    <t>6513</t>
+  </si>
+  <si>
+    <t>李承州</t>
+  </si>
+  <si>
+    <t>羹香鴨肉羹：乾麵 (小)*1 鴨肉羹 (小)*1</t>
+  </si>
+  <si>
+    <t>小菜項目：無 / 醬料/辣度：加醋 / 總計：$90</t>
   </si>
   <si>
     <t>店家/品項名稱</t>
@@ -102,10 +183,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -485,6 +569,136 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1785282817238</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1785282957055</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1785283551405</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>1785283576181</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>1785284199702</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="3">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -493,7 +707,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -502,10 +716,50 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/public/訂單統計表.xlsx
+++ b/public/訂單統計表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="63">
   <si>
     <t>訂單ID</t>
   </si>
@@ -117,6 +117,84 @@
   </si>
   <si>
     <t>小菜項目：無 / 醬料/辣度：加醋 / 總計：$90</t>
+  </si>
+  <si>
+    <t>2026/7/30 下午5:35:00</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：乾麵*1 鮮蝦紅油抄手 🌶️*1 滷豬心*1</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>食用方式：外帶 / 辣度：不辣</t>
+  </si>
+  <si>
+    <t>2026/7/30 下午6:43:42</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：原味餛飩麵 (湯)*1</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午7:05:27</t>
+  </si>
+  <si>
+    <t>17020</t>
+  </si>
+  <si>
+    <t>黃泓耀</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：滷肉飯*1 煙燻豬頭皮*1 滷豬舌*1 滷蛋 (顆)*1</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午7:08:09</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：香菇餛飩湯*1 滷肉飯*1 涼拌豆干絲*1 滷豬心*1</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午8:17:30</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：香菇餛飩湯*1 紅油抄手 🌶️*1 當季燙青菜*1 滷豬心*1</t>
+  </si>
+  <si>
+    <t>辣度：不辣</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午8:18:42</t>
+  </si>
+  <si>
+    <t>601207</t>
+  </si>
+  <si>
+    <t>郭勝明</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：乾麵*1 紅油抄手 🌶️*1</t>
+  </si>
+  <si>
+    <t>辣度：小辣</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午8:26:37</t>
+  </si>
+  <si>
+    <t>601473</t>
+  </si>
+  <si>
+    <t>李羽茹</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：原味餛飩湯*1 滷肉飯*1</t>
+  </si>
+  <si>
+    <t>2026/7/31 上午8:38:40</t>
+  </si>
+  <si>
+    <t>八鮮雲吞：原味餛飩湯*1</t>
   </si>
   <si>
     <t>店家/品項名稱</t>
@@ -531,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -699,6 +777,214 @@
         <v>90</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>1785404100845</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>1785408222307</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>1785452727694</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1785452889587</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>1785457050521</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>1785457122087</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>1785457597412</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>1785458320358</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="3">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -707,7 +993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -716,10 +1002,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -759,6 +1045,70 @@
         <v>33</v>
       </c>
       <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="3">
         <v>1</v>
       </c>
     </row>
